--- a/tabtools/demo/demo_effecttab.xlsx
+++ b/tabtools/demo/demo_effecttab.xlsx
@@ -304,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -315,6 +315,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -323,6 +327,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -379,6 +387,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -416,11 +428,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -455,16 +467,20 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -472,19 +488,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -527,87 +543,87 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="22" t="s">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="37" t="s">
+      <c r="A4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="43" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="38" t="s">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="45" t="s">
         <v>12</v>
       </c>
     </row>
@@ -635,137 +651,137 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="21" t="s">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="21" t="s">
+      <c r="D2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="22" t="s">
+      <c r="G2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="37" t="s">
+      <c r="A4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="43" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="46" t="s">
+      <c r="E5" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="46" t="s">
+      <c r="H5" s="50" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="55" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="0"/>
@@ -798,104 +814,104 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="22" t="s">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="37" t="s">
+      <c r="A4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="39" t="s">
+      <c r="C4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="37" t="s">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="38" t="s">
+      <c r="A6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="45" t="s">
         <v>12</v>
       </c>
     </row>
@@ -920,143 +936,143 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="22" t="s">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="37" t="s">
+      <c r="A4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="43" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="37" t="s">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="43" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="37" t="s">
+      <c r="A6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="43" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="37" t="s">
+      <c r="A7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="43" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="38" t="s">
+      <c r="A8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="45" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="55" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="0"/>

--- a/tabtools/demo/demo_effecttab.xlsx
+++ b/tabtools/demo/demo_effecttab.xlsx
@@ -10,13 +10,14 @@
     <sheet name="ATE Comparison" sheetId="2" r:id="rId4"/>
     <sheet name="Margins" sheetId="3" r:id="rId5"/>
     <sheet name="Margins AME" sheetId="4" r:id="rId6"/>
+    <sheet name="ATE cformat" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="137" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="162" uniqueCount="50">
   <si>
     <t>Table 6. Average Treatment Effect on CV Events (IPW)</t>
   </si>
@@ -33,109 +34,139 @@
     <t>ATE</t>
   </si>
   <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>95% CI</t>
+  </si>
+  <si>
+    <t>(-0.00, 0.05)</t>
+  </si>
+  <si>
+    <t>(0.33, 0.36)</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>Table 7. Treatment Effect Estimates -- IPW vs AIPW</t>
+  </si>
+  <si>
+    <t>IPW</t>
+  </si>
+  <si>
+    <t>AIPW</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>IPW = inverse probability weighting. AIPW = augmented IPW (doubly robust).</t>
+  </si>
+  <si>
+    <t>Table 8. Predicted Probability of CV Event by Treatment</t>
+  </si>
+  <si>
+    <t>Treatment group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SSRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SNRI</t>
+  </si>
+  <si>
+    <t>Pr(CV Event)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>(0.34, 0.37)</t>
+  </si>
+  <si>
+    <t>Table 9. Average Marginal Effects on CV Event Risk</t>
+  </si>
+  <si>
+    <t>Age at cohort entry (years)</t>
+  </si>
+  <si>
+    <t>Female sex</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>Hypertension</t>
+  </si>
+  <si>
+    <t>AME</t>
+  </si>
+  <si>
     <t>0.01</t>
   </si>
   <si>
-    <t>0.35</t>
-  </si>
-  <si>
-    <t>95% CI</t>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>(-0.01, 0.03)</t>
+  </si>
+  <si>
+    <t>(-0.00, 0.00)</t>
   </si>
   <si>
     <t>(-0.01, 0.02)</t>
   </si>
   <si>
-    <t>(0.34, 0.36)</t>
-  </si>
-  <si>
-    <t>p-value</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>&lt;0.001</t>
-  </si>
-  <si>
-    <t>Table 7. Treatment Effect Estimates -- IPW vs AIPW</t>
-  </si>
-  <si>
-    <t>IPW</t>
-  </si>
-  <si>
-    <t>AIPW</t>
-  </si>
-  <si>
-    <t>IPW = inverse probability weighting. AIPW = augmented IPW (doubly robust).</t>
-  </si>
-  <si>
-    <t>Table 8. Predicted Probability of CV Event by Treatment</t>
-  </si>
-  <si>
-    <t>Treatment group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SSRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SNRI</t>
-  </si>
-  <si>
-    <t>Pr(CV Event)</t>
-  </si>
-  <si>
-    <t>(0.34, 0.37)</t>
-  </si>
-  <si>
-    <t>Table 9. Average Marginal Effects on CV Event Risk</t>
-  </si>
-  <si>
-    <t>Age at cohort entry (years)</t>
-  </si>
-  <si>
-    <t>Female sex</t>
-  </si>
-  <si>
-    <t>Diabetes</t>
-  </si>
-  <si>
-    <t>Hypertension</t>
-  </si>
-  <si>
-    <t>AME</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>(0.00, 0.00)</t>
-  </si>
-  <si>
-    <t>(0.01, 0.04)</t>
+    <t>(0.00, 0.03)</t>
   </si>
   <si>
     <t>(-0.02, 0.01)</t>
   </si>
   <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>0.87</t>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>0.57</t>
   </si>
   <si>
     <t>AME = average marginal effect. Change in Pr(CV event) per unit change in covariate.</t>
+  </si>
+  <si>
+    <t>Table 6b. Average Treatment Effect, Four Decimals</t>
+  </si>
+  <si>
+    <t>0.0233</t>
+  </si>
+  <si>
+    <t>0.3448</t>
+  </si>
+  <si>
+    <t>(-0.0020, 0.0487)</t>
+  </si>
+  <si>
+    <t>(0.3317, 0.3579)</t>
   </si>
 </sst>
 </file>
@@ -268,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -330,9 +361,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="general" vertical="top" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
@@ -610,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -641,7 +669,7 @@
     </row>
     <row r="6">
       <c r="B6" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="0"/>
       <c r="D6" s="0"/>
@@ -674,7 +702,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -714,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>7</v>
@@ -728,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1</v>
@@ -745,10 +773,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>9</v>
@@ -762,13 +790,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>12</v>
@@ -795,144 +823,144 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="37" t="s">
+      <c r="A1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="27" t="s">
+      <c r="C6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="29" t="s">
+      <c r="C8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="D8" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="E8" s="9" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="s">
-        <v>39</v>
+      <c r="B9" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="C9" s="0"/>
       <c r="D9" s="0"/>
@@ -945,4 +973,109 @@
     <mergeCell ref="B9:E9"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="16.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="8.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="17.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="8.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C2:E2"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/tabtools/demo/demo_effecttab.xlsx
+++ b/tabtools/demo/demo_effecttab.xlsx
@@ -43,7 +43,7 @@
     <t>95% CI</t>
   </si>
   <si>
-    <t>(-0.00, 0.05)</t>
+    <t>(0.00, 0.05)</t>
   </si>
   <si>
     <t>(0.33, 0.36)</t>
@@ -124,7 +124,7 @@
     <t>(-0.01, 0.03)</t>
   </si>
   <si>
-    <t>(-0.00, 0.00)</t>
+    <t>(0.00, 0.00)</t>
   </si>
   <si>
     <t>(-0.01, 0.02)</t>
